--- a/internal/test/excels/enum.xlsx
+++ b/internal/test/excels/enum.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13380"/>
+    <workbookView windowWidth="29100" windowHeight="13420"/>
   </bookViews>
   <sheets>
     <sheet name="全局枚举表|Enum" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>类型/值</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>c/s</t>
+  </si>
   <si>
     <t>ItemType_BEGIN</t>
   </si>
@@ -66,6 +81,18 @@
   </si>
   <si>
     <t>钻石</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>TestClientEnum_BEGIN</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -425,12 +452,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -557,7 +599,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -569,34 +611,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -681,8 +723,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1217,77 +1262,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="22.6923076923077" customWidth="1"/>
-    <col min="3" max="3" width="12.7692307692308" customWidth="1"/>
+    <col min="2" max="2" width="25.7692307692308" customWidth="1"/>
+    <col min="4" max="4" width="12.7692307692308" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>8</v>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
         <v>0</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
+      <c r="D8" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
